--- a/docs/ptx-compat-requirements.xlsx
+++ b/docs/ptx-compat-requirements.xlsx
@@ -7,11 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="三层依赖表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="④device层_ISA要求" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="落地策略与约束" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="先读导图" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="三层依赖表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="④device层_ISA要求" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="落地策略与约束" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="术语表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="验证检查清单" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'先读导图'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三层依赖表'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'④device层_ISA要求'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'落地策略与约束'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'术语表'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'验证检查清单'!$A$1:$D$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +42,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +71,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,21 +115,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -469,6 +506,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>新手版解释</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>对应表 / 文档</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一句话</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PyTorch 发起 all_reduce；NCCL host 侧选择算法并准备任务单；GPU device kernel 负责跨卡搬数据和归约。</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>docs/allreduce-deep-dive.md §给 NCCL 小白的速读版</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>先看哪张表</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>先读本页，再看“三层依赖表”判断要实现哪些 host/runtime 能力；最后看“④device层_ISA要求”和“验证检查清单”。</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>本工作簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>三段心智模型</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>① ATen/PyTorch 负责入口；② NCCL/pccl 负责 API、调度、构造 ncclWork；③ Runtime 负责 launch 和跨卡内存；④ device PTX 真正执行。</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>三层依赖表 / ④device层_ISA要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>barrier 为什么也出现</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NCCL 没有独立 ncclBarrier；PyTorch barrier 用 1 元素 tensor 跑一次 AllReduce，所以会看到 AllReduce kernel。</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>allreduce-deep-dive.md §barrier 变体</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>实测主线</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>双卡 Qwen3-8B trace 里，f16 all_reduce 和 f32 barrier 都选中 RING+LL；差异主要是 count/grid/block。</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>落地策略与约束 / allreduce-deep-dive.md §7.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>最容易踩坑</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>不是所有 NCCL 内部函数都必须照抄，但最终写给 device 的结构体布局、channelMask、P2P ring buffer、smem/block 必须和 PTX 期待一致。</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>验证检查清单</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -518,734 +694,735 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>① ATen
 (torch算子分发)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>torch op</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>c10d::allreduce_</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>trace[aten] / doc L2</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>all_reduce 分发:校验单 tensor、复数→view_as_real、节点内 SHMEM 快速路径否则走 NCCL</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>sunrise torch 构建需注册此 op,路由到 pccl</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>① ATen
 (torch算子分发)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>torch op</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>c10d::barrier</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>trace[aten] / doc §barrier变体</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>barrier 分发;内部 allreduce_impl(barrierTensor_) 复用 AllReduce 机器</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>同上,路由到 pccl(走 allreduce)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>① ATen
 (torch算子分发)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>torch op</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>record_param_comms</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>trace[aten]</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>param↔comms 映射,profiling/DTENSOR 用</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>仅为 trace 完整,非功能路径</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>公共API(必须导出)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ncclAllReduce(sendbuff,recvbuff,count,datatype,op,comm,stream)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>NCCL C API 入口;构造 ncclInfo 后调 ncclEnqueueCheck</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>pccl 同名同签名实现</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>公共API(必须导出)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>ncclGetUniqueId / ncclCommInitRank / ncclCommInitAll</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>doc 12.1(前置)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>communicator 初始化,建 rank/nRanks/channel 拓扑</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>pccl 必须提供(构造等价 devComm)</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>公共API(必须导出)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>枚举 ncclDataType_t / ncclRedOp_t / ncclComm_t</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>doc 3.3</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>类型与归约操作枚举(torch 侧 getNcclDataType/getNcclReduceOp 依赖其值)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>pccl 需兼容这套枚举值</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>host内部(自研等价/复用白送)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ncclEnqueueCheck</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L5</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>group 语义、comm/参数校验、调 taskAppend</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>pccl 内部等价</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>必选*</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>host内部(自研等价/复用白送)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>taskAppend (+hostToDevRedOp)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L5</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>ncclSum→ncclDevSum 转换;单 rank memcpy 快速路径;多 rank 入 collQueue</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>pccl 内部等价</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>必选*</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>host内部(自研等价/复用白送)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>scheduleCollTasksToPlan (+topoGetAlgoInfo/ncclDevFuncId/initCollWorkElem/uploadWork/getChannnelThreadInfo/computeCollChunkInfo/getPatternInfo)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L6</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>选 algo×proto(实测 RING+LL)、算 channel/线程、填 ncclWorkElem、上传 workFifo</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>pccl 内部等价;必须产出与 PTX 期望一致的 devComm/ncclWork/channelMask 布局</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>必选*</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>host内部(自研等价/复用白送)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>ncclLaunchKernel (+ncclShmemDynamicSize)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L7</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>设 grid/block/smem、组 3 参数 {&amp;devComm,&amp;channelMask,&amp;workHead}、调 cudaLaunchKernelExC</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>pccl 内部等价</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>必选*</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>② NCCL→pccl
 (链接库)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>host内部(自研等价/复用白送)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>ncclGroupStart / ncclGroupEnd</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>doc L5</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>group 批提交语义</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>pccl 内部等价</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>必选*</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>cudaLaunchKernelExC / cudaLaunchKernel</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>trace[launch] / doc L7</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>启动 kernel(含 cudaLaunchConfig_t:grid/block/dynamicSmemBytes/stream)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>cudaStream_t + cudaEvent + syncStream</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>trace[runtime] / doc L3</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>专用 comms stream、与计算 stream 异步同步</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>cuModuleLoadData + cuModuleGetFunction</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>doc 12.2</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>加载转译后的 PTX、取 kernel 句柄</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持(PTX/SASS 加载)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>cuLaunchKernel</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>doc 12.2</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>driver 级 launch</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>cuMemAlloc / cuMemcpyHtoD (cudaMalloc/cudaMemcpy)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>doc 12.2</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>分配并填充 devComm/channel/work/sendbuff/recvbuff/abortFlag</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>P2P: cudaDeviceEnablePeerAccess / peer memory mapping</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>doc 12.3 注②</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>跨 GPU ring buffer 的 ld/st.volatile.global 读写(NVLink/PCIe P2P)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>sunrise 硬件/驱动必须支持跨卡 P2P 内存映射(关键)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>必选(关键)</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>cudaFuncSetAttribute(MaxDynamicSharedMemorySize)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>doc L7/12.2</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>申请 88416 B 动态 shared mem</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>③ Runtime
 (sunrise runtime)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>CUDA runtime/driver</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>cudaCtxSynchronize / stream sync</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>doc 12.2</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>同步收尾</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>sunrise runtime 必须支持</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1282,122 +1459,123 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>翻译目标</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>.visible .entry ncclDevKernel_AllReduce_Sum_{f16,f32}_RING_LL</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>nccl_ptx/*.ptx / doc L8</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>已 inline 了 ncclKernelMain / RunWork::run / runRing / ProtoLL,PTX 里只剩此一个 entry</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ISA要求</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ld/st.volatile.global (跨卡 P2P)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>doc 10.5/12.3 注②</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>读写 peer GPU 的 ring buffer;对应第③层 P2P 映射</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ISA要求</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>bar.sync 0 + bar.sync %r,%n (warp 分工形式)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>doc 9.2/12.3 注③</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>线程数非固定(LL 上限 512,barrier 调谐到 96)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ISA要求</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>__popcll</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>doc 9.2 阶段1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>channelMask(64-bit 位图)→channelId 映射</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ABI要求</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>静态 ncclShmem layout 二进制兼容</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>doc 12.3 注①</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>host 填的 ncclDevComm/ncclWork 结构体布局必须与 PTX 读取一致</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1422,79 +1600,528 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>策略1: Drop-in 替换</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>pccl 只实现第②层公共 API(ncclAllReduce+ncclComm*+枚举),内部自研。ncclEnqueueCheck~ncclLaunchKernel 不用逐个照抄(表中标*的),只要最终产出布局兼容的 devComm/ncclWork 并 launch。工作量小,但要自己保证 device 结构体 ABI 与 PTX 一致。</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>策略2: 复用 NCCL host + 换 device PTX</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>host 全留(第②层内部白送,标*的全部白送),sunrise 只补第③层 runtime 和第④层 PTX 转译。工作量最小,但要求 sunrise runtime 能被 NCCL host 当 CUDA runtime 用。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>跨层硬约束1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>第②层填进 device memory 的 ncclDevComm/ncclWork/channelMask 布局,必须和第④层 PTX 里读这些结构的指令严丝合缝。</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>跨层硬约束2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>barrier 路径与 all_reduce 共用第②③④层,只是入口 aten op 不同(c10d::barrier vs c10d::allreduce_)。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>实测依据</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>双卡 Qwen3-8B trace:① f16 RING_LL (MLP all_reduce, shape=[1,16,4096], grid=[16,1,1], block=[512,1,1], smem=88416);② f32 RING_LL (barrier, count=1, grid=[1,1,1], block=[96,1,1], smem=88416)。本地构建只特化了 LL。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>必选=功能路径必需;可选=仅 trace/profiling;必选*=Drop-in 策略下 pccl 自研需等价实现,复用 NCCL host 策略下白送。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>术语</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>一句话理解</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>为什么重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AllReduce</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>每张 GPU 先各有一份数据；调用后，每张 GPU 都拿到所有 rank 归约后的完整结果。</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>训练里常用于梯度求和/平均，是本次 PTX 链路的 collective 类型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>通信组里的 GPU 编号；双卡时通常是 rank 0 和 rank 1。</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ring/tree 拓扑、prev/next、buffer 地址都按 rank 组织。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>communicator / ncclComm</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>一组 GPU 的通信上下文，记录 rank 数、拓扑、channel、device 侧结构体地址等。</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PyTorch 每次 all_reduce 最终都要拿到一个 comm 才能调用 ncclAllReduce。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NCCL 把一次大通信拆成多条并行“车道”。</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>实测 f16 all_reduce 用 16 个 channel，所以 grid.x=16；barrier 只用 1 个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>algo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>通信拓扑算法，例如 RING、TREE、NVLS。</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>algo 决定 device 端走 runRing 还是 runTree；本次实测选中 RING。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>通信协议，例如 LL、LL128、SIMPLE。</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>proto 决定底层搬运方式；本地 used-only PTX 是 LL 特化 kernel。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ncclWork / ncclWorkElem</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>host 写给 device kernel 的任务单，里面有 send/recv buffer、count、chunk、funcIndex 等。</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>pccl 自研 host 时不必照抄 NCCL 函数名，但必须生成 PTX 能读懂的任务单布局。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>channelMask</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>64-bit 位图，哪个 bit 为 1 就代表哪个 channel 参与本次 kernel。</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>kernel 内部用 __popcll 把 blockIdx.x 映射到真实 channelId。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P2P memory mapping</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>一张 GPU 能直接访问另一张 GPU 暴露出来的 ring buffer。</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Ring LL 的 ld/st.volatile.global 依赖这个能力完成跨卡通信。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>dynamic shared memory / smem</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>launch kernel 时额外申请的 shared memory 字节数。</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>实测 RING_LL 也需要约 88416 B；不能简单以为 LL 就是 0。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>通过标准</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>对应依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NCCL 公共 API 兼容</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>能导出并链接 ncclAllReduce、ncclGetUniqueId、ncclCommInitRank/All，以及兼容的 datatype/reduce op 枚举。</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>三层依赖表: ② 公共API</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AllReduce 参数语义正确</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>count 按元素数而不是字节数解释；sendbuff/recvbuff 支持 in-place；stream 异步语义保持。</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>allreduce-deep-dive.md §5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>device 结构体 ABI 兼容</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ncclDevComm、ncclDevChannel、ncclWork、ncclWorkElem 的字段偏移与 PTX 读取一致。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>④device层_ISA要求 / allreduce-deep-dive.md §11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>P2P ring buffer 可访问</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>peer GPU buffer 能被本 GPU 通过 global memory load/store 访问，volatile 读写语义正确。</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>④device层_ISA要求: ld/st.volatile.global</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>kernel launch 参数一致</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>传入 3 个参数 {devComm, channelMask, workHead}；grid.x=popcount(channelMask)；block/smem 与调度结果一致。</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>allreduce-deep-dive.md §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>RING+LL 路径可跑通</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>至少复现实测 f16 all_reduce: grid=16、block=512、smem≈88416；以及 f32 barrier: grid=1、block=96。</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>落地策略与约束: 实测依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>barrier 复用 AllReduce</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>torch barrier 最终能走 count=1 的 ncclAllReduce，不需要虚构 ncclBarrier。</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>allreduce-deep-dive.md §barrier 变体</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PTX ISA 覆盖</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>支持 __popcll、bar.sync 0、bar.sync %r,%n、ld/st.volatile.global 以及 shared/global 地址转换。</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>④device层_ISA要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Generic kernel 边界清楚</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>LL128/SIMPLE 不误用 RING_LL 特化 entry；需要时改走 ncclDevKernel_Generic。</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>allreduce-deep-dive.md §12.3 注意事项</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>